--- a/EXCEL/Data/Køn_data/køn_overenskomst.xlsx
+++ b/EXCEL/Data/Køn_data/køn_overenskomst.xlsx
@@ -76,7 +76,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 13.57.52</t>
+    <t>Kørsel 14.4.2026 12.27.50</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
